--- a/output/pdf_financials_xlsx/CLUS.xlsx
+++ b/output/pdf_financials_xlsx/CLUS.xlsx
@@ -2970,19 +2970,19 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1575</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.1575</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.417836</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.417836</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.417836</v>
       </c>
     </row>
     <row r="93">
@@ -4668,7 +4668,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 5)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5026,7 +5030,11 @@
           <t>SHARE-BASED PAYMENT RESERVE (Note 5)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CLUS.xlsx
+++ b/output/pdf_financials_xlsx/CLUS.xlsx
@@ -1336,19 +1336,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.305255</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.051207</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.109853</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.00139</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001567</v>
       </c>
     </row>
     <row r="35">
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.305255</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.051207</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.109853</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.00139</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001567</v>
       </c>
     </row>
     <row r="37">
@@ -1717,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.12578</v>
+        <v>0.074573</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.127428</v>
+        <v>0.017575</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.8e-05</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/CLUS.xlsx
+++ b/output/pdf_financials_xlsx/CLUS.xlsx
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006392</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002874</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.018385</v>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.035772</v>
+        <v>0.02938</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.090062</v>
@@ -6308,7 +6308,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
